--- a/data/trans_bre/IP2005-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 9,12</t>
+          <t>-3,2; 9,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 3,41</t>
+          <t>-8,52; 3,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 9,38</t>
+          <t>-3,79; 9,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 1,88</t>
+          <t>-13,2; 2,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 10,65</t>
+          <t>-3,38; 10,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 3,76</t>
+          <t>-8,74; 4,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 10,74</t>
+          <t>-3,96; 10,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 2,13</t>
+          <t>-14,26; 3,07</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 7,56</t>
+          <t>-6,25; 7,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 0,58</t>
+          <t>-10,39; 1,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 7,85</t>
+          <t>-3,06; 7,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 5,96</t>
+          <t>-10,37; 6,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 8,81</t>
+          <t>-6,67; 8,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 0,58</t>
+          <t>-10,79; 1,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 8,95</t>
+          <t>-3,19; 8,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 7,07</t>
+          <t>-11,72; 7,88</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 6,11</t>
+          <t>-8,83; 7,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 4,06</t>
+          <t>-12,09; 2,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 7,82</t>
+          <t>-6,95; 6,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 15,15</t>
+          <t>-7,18; 13,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 6,94</t>
+          <t>-9,74; 8,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 4,58</t>
+          <t>-12,98; 3,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 8,62</t>
+          <t>-7,1; 7,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 18,59</t>
+          <t>-7,56; 17,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 5,12</t>
+          <t>-6,06; 4,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 1,51</t>
+          <t>-7,36; 1,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 7,78</t>
+          <t>-2,05; 7,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 9,52</t>
+          <t>-2,68; 9,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 6,06</t>
+          <t>-6,76; 5,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 1,7</t>
+          <t>-7,85; 1,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 9,12</t>
+          <t>-2,24; 9,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 11,48</t>
+          <t>-3,05; 11,49</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 7,6</t>
+          <t>-5,5; 8,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 8,39</t>
+          <t>-5,52; 8,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 8,93</t>
+          <t>-1,61; 9,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 3,82</t>
+          <t>-10,21; 3,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 9,16</t>
+          <t>-6,16; 9,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 10,25</t>
+          <t>-6,09; 10,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 10,38</t>
+          <t>-1,78; 10,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 4,36</t>
+          <t>-10,95; 4,08</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,58</t>
+          <t>-6,86; 4,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,04; 17,92</t>
+          <t>2,29; 18,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 4,07</t>
+          <t>-10,45; 3,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 12,94</t>
+          <t>-6,6; 12,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 4,87</t>
+          <t>-6,98; 4,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,27; 22,28</t>
+          <t>2,51; 22,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 4,29</t>
+          <t>-10,63; 3,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 15,95</t>
+          <t>-7,04; 15,14</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,09</t>
+          <t>-2,39; 3,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 1,47</t>
+          <t>-3,82; 1,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,27</t>
+          <t>-0,45; 4,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 2,99</t>
+          <t>-3,69; 2,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 3,5</t>
+          <t>-2,63; 3,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 1,62</t>
+          <t>-4,13; 1,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,78</t>
+          <t>-0,48; 5,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,43</t>
+          <t>-4,07; 3,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 9,05</t>
+          <t>-3,91; 9,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 3,82</t>
+          <t>-8,17; 4,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 9,56</t>
+          <t>-3,32; 10,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 2,51</t>
+          <t>-13,81; 1,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 10,51</t>
+          <t>-4,13; 10,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 4,13</t>
+          <t>-8,47; 4,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 10,86</t>
+          <t>-3,46; 11,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 3,07</t>
+          <t>-15,06; 1,54</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 7,82</t>
+          <t>-6,29; 7,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 1,4</t>
+          <t>-10,35; 1,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,97</t>
+          <t>-2,5; 8,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 6,48</t>
+          <t>-10,93; 6,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 8,9</t>
+          <t>-6,7; 8,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 1,36</t>
+          <t>-10,64; 1,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 8,98</t>
+          <t>-2,57; 9,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 7,88</t>
+          <t>-12,05; 7,61</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 7,31</t>
+          <t>-9,21; 6,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 2,83</t>
+          <t>-12,29; 3,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 6,82</t>
+          <t>-7,0; 6,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 13,81</t>
+          <t>-6,95; 13,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 8,35</t>
+          <t>-9,85; 7,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 3,08</t>
+          <t>-12,76; 3,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 7,49</t>
+          <t>-7,23; 7,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 17,37</t>
+          <t>-7,43; 16,24</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 4,66</t>
+          <t>-6,05; 5,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 1,68</t>
+          <t>-7,25; 2,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 7,99</t>
+          <t>-1,52; 8,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 9,62</t>
+          <t>-2,8; 9,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,45</t>
+          <t>-6,72; 5,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 1,85</t>
+          <t>-7,68; 2,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 9,38</t>
+          <t>-1,69; 9,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 11,49</t>
+          <t>-3,24; 11,79</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 8,33</t>
+          <t>-6,01; 7,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 8,62</t>
+          <t>-5,77; 8,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 9,36</t>
+          <t>-2,03; 9,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 3,66</t>
+          <t>-9,98; 3,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 9,99</t>
+          <t>-6,58; 9,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 10,77</t>
+          <t>-6,38; 10,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 10,86</t>
+          <t>-2,15; 10,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 4,08</t>
+          <t>-10,78; 4,36</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 4,6</t>
+          <t>-6,76; 4,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 18,16</t>
+          <t>3,23; 17,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 3,68</t>
+          <t>-9,45; 4,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 12,3</t>
+          <t>-6,3; 12,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 4,96</t>
+          <t>-6,93; 5,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 22,86</t>
+          <t>3,54; 21,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 3,87</t>
+          <t>-9,57; 4,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 15,14</t>
+          <t>-6,67; 15,83</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,12</t>
+          <t>-2,49; 2,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,45</t>
+          <t>-3,75; 1,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,57</t>
+          <t>-0,37; 4,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,75</t>
+          <t>-3,65; 2,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,52</t>
+          <t>-2,71; 3,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,6</t>
+          <t>-4,06; 1,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,11</t>
+          <t>-0,4; 4,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 3,14</t>
+          <t>-4,04; 3,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,6</t>
+          <t>-5,46</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,26%</t>
+          <t>-6,12%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 9,23</t>
+          <t>-3,6; 9,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 4,06</t>
+          <t>-8,8; 3,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 10,15</t>
+          <t>-3,31; 9,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 1,39</t>
+          <t>-13,65; 1,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 10,74</t>
+          <t>-3,85; 10,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 4,25</t>
+          <t>-8,99; 3,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 11,66</t>
+          <t>-3,4; 10,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 1,54</t>
+          <t>-14,88; 2,0</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,46</t>
+          <t>-2,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-2,82%</t>
+          <t>-3,06%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 7,6</t>
+          <t>-6,72; 7,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 1,46</t>
+          <t>-10,62; 0,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 8,7</t>
+          <t>-2,8; 7,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 6,43</t>
+          <t>-11,66; 5,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 8,8</t>
+          <t>-7,13; 8,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 1,53</t>
+          <t>-10,95; 0,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 9,86</t>
+          <t>-2,91; 8,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 7,61</t>
+          <t>-12,73; 6,77</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>3,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 6,63</t>
+          <t>-9,11; 6,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 3,31</t>
+          <t>-10,81; 4,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 6,58</t>
+          <t>-5,88; 7,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 13,46</t>
+          <t>-5,82; 14,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 7,59</t>
+          <t>-9,8; 6,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 3,74</t>
+          <t>-11,34; 4,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 7,31</t>
+          <t>-6,14; 8,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 16,24</t>
+          <t>-6,23; 18,25</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>1,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 5,01</t>
+          <t>-5,82; 5,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 2,2</t>
+          <t>-7,81; 1,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 8,23</t>
+          <t>-1,86; 7,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 9,83</t>
+          <t>-4,22; 8,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 5,83</t>
+          <t>-6,37; 6,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 2,44</t>
+          <t>-8,22; 1,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 9,76</t>
+          <t>-2,05; 9,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 11,79</t>
+          <t>-4,75; 10,08</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,11</t>
+          <t>-3,31</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-3,42%</t>
+          <t>-3,64%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 7,6</t>
+          <t>-6,04; 7,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 8,25</t>
+          <t>-5,55; 8,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 9,26</t>
+          <t>-2,07; 8,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 3,87</t>
+          <t>-10,48; 3,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 9,03</t>
+          <t>-6,77; 9,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 10,13</t>
+          <t>-6,19; 10,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 10,68</t>
+          <t>-2,25; 10,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 4,36</t>
+          <t>-11,17; 4,29</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 4,92</t>
+          <t>-6,32; 4,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 17,28</t>
+          <t>3,04; 17,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 4,08</t>
+          <t>-9,53; 4,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 12,76</t>
+          <t>-7,3; 11,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 5,25</t>
+          <t>-6,64; 4,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 21,49</t>
+          <t>3,27; 22,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 4,43</t>
+          <t>-9,87; 4,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 15,83</t>
+          <t>-7,76; 13,81</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-1,1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-0,57%</t>
+          <t>-1,25%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,87</t>
+          <t>-2,36; 3,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,59</t>
+          <t>-3,83; 1,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,29</t>
+          <t>-0,47; 4,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 2,92</t>
+          <t>-4,31; 2,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,26</t>
+          <t>-2,59; 3,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,75</t>
+          <t>-4,12; 1,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,76</t>
+          <t>-0,52; 4,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 3,34</t>
+          <t>-4,8; 2,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,25</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,03</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,24</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,46</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-2,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-6,12%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.246422445563978</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.029178207179982</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.237086951105617</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-5.463588506151673</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.02472487519643131</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.02133978199279613</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.03525881059156414</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.06122495434537899</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,6; 9,12</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,8; 3,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,31; 9,38</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-13,65; 1,78</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-3,85; 10,65</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-8,99; 3,76</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-3,4; 10,74</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-14,88; 2,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.603008605599958</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.799880846855407</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.308715487535618</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-13.64832670444437</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.03848326439120823</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.08994004201067775</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.03398460450773941</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1487790967086884</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.12321790852735</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.412022693824927</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.375968630479687</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.783245340970265</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1064921655924745</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.03762741048373711</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.107445694726871</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.02003995339562001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-4,2</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,37</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-4,36%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-3,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,72; 7,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-10,62; 0,58</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,8; 7,85</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,66; 5,58</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-7,13; 8,81</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-10,95; 0,58</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-2,91; 8,95</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-12,73; 6,77</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.8537712833386113</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-4.204188633108097</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.367504969738798</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.67427906259603</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.009393215953726695</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.04355835545047906</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.02548862068021326</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.03059802203016705</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,94</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,23</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-4,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.72021479947351</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-10.61851045941695</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.798564520401496</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.66197308644107</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.07134779913135583</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1094697817212225</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.02910173412922472</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1272771546161617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,11; 6,11</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,81; 4,06</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,88; 7,82</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,82; 14,34</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-9,8; 6,94</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-11,34; 4,58</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-6,14; 8,62</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-6,23; 18,25</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.56360538349074</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5824048988425433</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.851932848645504</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.581502834418806</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.08807908325081533</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.005807924541363394</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.0895248382869847</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.06773161683016103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,71</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,96</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,64</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,55%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-2,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.093771927648646</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.936350273360201</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1605697870000866</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3.225357122344374</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.01209800417413021</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.0428637380716486</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.001706808757164064</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.03655355031828789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,82; 5,12</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-7,81; 1,51</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,86; 7,78</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,22; 8,16</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-6,37; 6,06</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-8,22; 1,7</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-2,05; 9,12</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-4,75; 10,08</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.109869246252114</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.81254111751912</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.876983325980969</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.816088234317606</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.09800928047962804</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1134097337095188</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.06141041533059368</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.06225094364446652</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.108792220007399</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.055730515447549</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.815370761623059</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>14.3374164597515</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.06942982144841044</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.0457751075203535</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.08621377989981968</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.1824553383791745</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,31</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-3,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-6,04; 7,6</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,55; 8,39</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,07; 8,93</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-10,48; 3,93</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-6,77; 9,16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-6,19; 10,25</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-2,25; 10,38</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-11,17; 4,29</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.4880600426104276</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.707185843987714</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.958771708001828</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.639184103034474</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.005549555567084056</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.02916292545136598</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.03360715824138103</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.01908161658000177</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9,89</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-2,87</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-1,18%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-2,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.817063436034265</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-7.813772338870248</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.856083671565043</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.224478127488125</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.06367727049621649</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.08222848456820242</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.02053370767763397</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.04748956023838428</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-6,32; 4,58</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3,04; 17,92</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-9,53; 4,07</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-7,3; 11,54</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-6,64; 4,87</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>3,27; 22,28</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-9,87; 4,29</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-7,76; 13,81</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.118105443576402</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.514329625518992</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.77602478132456</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>8.157201397730237</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.06063685103743199</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.01704239966928374</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.09122697221002603</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.1007861225151784</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-1,14</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-1,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-1,25%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>1.287724876852647</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.347634831085409</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.383028749489281</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3.311496582087459</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.01469767058950326</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.01566782957694315</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.03762660955532703</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.0364055343781098</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,36; 3,09</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,83; 1,47</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 4,27</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-4,31; 2,18</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-2,59; 3,5</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-4,12; 1,62</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-0,52; 4,78</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-4,8; 2,54</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-6.039468471313119</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.550441440940773</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.067594056280657</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-10.47899023251355</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.067665741443696</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.0618721234088977</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.02245701833151056</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.111706140583751</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.602208807680958</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>8.391975860130033</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>8.928279882620258</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.927304045433132</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.09161308424018356</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1024596603968184</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.1038015650497927</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.04293631749505114</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-1.130967391564608</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>9.889577483689738</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-2.865341633831464</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1.655520737519267</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.0118031316926811</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.1130574936014268</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.02981283119231343</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.01853837778263029</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-6.322607155111282</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3.042557742468785</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-9.534426438640839</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-7.295657762248671</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.066429664261115</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.0326800319067446</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.0986909291341001</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.07760244968329606</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>4.580274724149529</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>17.91650435021482</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>4.066899082911135</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>11.54069040831645</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.04873142914001534</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.2227851396078558</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.04288755462336549</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.1380685828706527</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.3738222180624251</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-1.137746223131697</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2.030434819373694</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.102719413927711</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.004160543010084217</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.01241657098236211</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.02228528994455375</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.01248585199655178</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.364889134748122</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.829000764341966</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.4698986166029501</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-4.311087009853116</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.0259029287593596</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.04124389088119703</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.005171434123759317</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.04800345733185896</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>3.089595877285298</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.470581398713639</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>4.274184746088546</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.180229529550946</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.03504531451017846</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.01618377606668663</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.0477912332424779</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.02544363916838205</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
